--- a/Data_clean/MCAS/Estados_US/Edos_USA_2022/WEST_VIRGINIA_2022.xlsx
+++ b/Data_clean/MCAS/Estados_US/Edos_USA_2022/WEST_VIRGINIA_2022.xlsx
@@ -351,28 +351,28 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D108"/>
+  <dimension ref="A1:D102"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Estado de Origen</t>
+          <t>mx_state</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Municipio Origen</t>
+          <t>mx_municipality</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>Número de Matrículas</t>
+          <t>n_matriculas</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>Porcentaje de Matrículas</t>
+          <t>pct_matriculas</t>
         </is>
       </c>
     </row>
@@ -395,6 +395,11 @@
       </c>
     </row>
     <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Aguascalientes</t>
+        </is>
+      </c>
       <c r="B3" t="inlineStr">
         <is>
           <t>Total</t>
@@ -426,6 +431,11 @@
       </c>
     </row>
     <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Baja California</t>
+        </is>
+      </c>
       <c r="B5" t="inlineStr">
         <is>
           <t>Total</t>
@@ -446,7 +456,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Amatenango de la Frontera</t>
+          <t>Amatenango De La Frontera</t>
         </is>
       </c>
       <c r="C6">
@@ -457,6 +467,11 @@
       </c>
     </row>
     <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B7" t="inlineStr">
         <is>
           <t>Chamula</t>
@@ -470,6 +485,11 @@
       </c>
     </row>
     <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B8" t="inlineStr">
         <is>
           <t>Chenalhó</t>
@@ -483,6 +503,11 @@
       </c>
     </row>
     <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B9" t="inlineStr">
         <is>
           <t>Escuintla</t>
@@ -496,6 +521,11 @@
       </c>
     </row>
     <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B10" t="inlineStr">
         <is>
           <t>Frontera Comalapa</t>
@@ -509,6 +539,11 @@
       </c>
     </row>
     <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B11" t="inlineStr">
         <is>
           <t>Las Margaritas</t>
@@ -522,6 +557,11 @@
       </c>
     </row>
     <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B12" t="inlineStr">
         <is>
           <t>Ostuacán</t>
@@ -535,6 +575,11 @@
       </c>
     </row>
     <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B13" t="inlineStr">
         <is>
           <t>Tapalapa</t>
@@ -548,6 +593,11 @@
       </c>
     </row>
     <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B14" t="inlineStr">
         <is>
           <t>Total</t>
@@ -563,7 +613,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Ciudad de México</t>
+          <t>Ciudad De México</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -579,6 +629,11 @@
       </c>
     </row>
     <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B16" t="inlineStr">
         <is>
           <t>Azcapotzalco</t>
@@ -592,6 +647,11 @@
       </c>
     </row>
     <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B17" t="inlineStr">
         <is>
           <t>Iztapalapa</t>
@@ -605,6 +665,11 @@
       </c>
     </row>
     <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B18" t="inlineStr">
         <is>
           <t>Total</t>
@@ -620,12 +685,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Estado de México</t>
+          <t>Estado De México</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Almoloya de Juárez</t>
+          <t>Almoloya De Juárez</t>
         </is>
       </c>
       <c r="C19">
@@ -636,6 +701,11 @@
       </c>
     </row>
     <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B20" t="inlineStr">
         <is>
           <t>Amatepec</t>
@@ -649,6 +719,11 @@
       </c>
     </row>
     <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B21" t="inlineStr">
         <is>
           <t>Nezahualcóyotl</t>
@@ -662,6 +737,11 @@
       </c>
     </row>
     <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B22" t="inlineStr">
         <is>
           <t>Sultepec</t>
@@ -675,6 +755,11 @@
       </c>
     </row>
     <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B23" t="inlineStr">
         <is>
           <t>Tejupilco</t>
@@ -688,6 +773,11 @@
       </c>
     </row>
     <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B24" t="inlineStr">
         <is>
           <t>Tlatlaya</t>
@@ -701,6 +791,11 @@
       </c>
     </row>
     <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B25" t="inlineStr">
         <is>
           <t>Total</t>
@@ -732,6 +827,11 @@
       </c>
     </row>
     <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B27" t="inlineStr">
         <is>
           <t>Total</t>
@@ -752,7 +852,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Alcozauca de Guerrero</t>
+          <t>Alcozauca De Guerrero</t>
         </is>
       </c>
       <c r="C28">
@@ -763,9 +863,14 @@
       </c>
     </row>
     <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Atoyac de Álvarez</t>
+          <t>Atoyac De Álvarez</t>
         </is>
       </c>
       <c r="C29">
@@ -776,9 +881,14 @@
       </c>
     </row>
     <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Chilapa de Álvarez</t>
+          <t>Chilapa De Álvarez</t>
         </is>
       </c>
       <c r="C30">
@@ -789,9 +899,14 @@
       </c>
     </row>
     <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Coyuca de Catalán</t>
+          <t>Coyuca De Catalán</t>
         </is>
       </c>
       <c r="C31">
@@ -802,6 +917,11 @@
       </c>
     </row>
     <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B32" t="inlineStr">
         <is>
           <t>Malinaltepec</t>
@@ -815,6 +935,11 @@
       </c>
     </row>
     <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B33" t="inlineStr">
         <is>
           <t>Petatlán</t>
@@ -828,6 +953,11 @@
       </c>
     </row>
     <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B34" t="inlineStr">
         <is>
           <t>Pungarabato</t>
@@ -841,6 +971,11 @@
       </c>
     </row>
     <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B35" t="inlineStr">
         <is>
           <t>Quechultenango</t>
@@ -854,6 +989,11 @@
       </c>
     </row>
     <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B36" t="inlineStr">
         <is>
           <t>San Miguel Totolapan</t>
@@ -867,9 +1007,14 @@
       </c>
     </row>
     <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Técpan de Galeana</t>
+          <t>Técpan De Galeana</t>
         </is>
       </c>
       <c r="C37">
@@ -880,6 +1025,11 @@
       </c>
     </row>
     <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B38" t="inlineStr">
         <is>
           <t>Total</t>
@@ -900,7 +1050,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Atotonilco el Grande</t>
+          <t>Atotonilco El Grande</t>
         </is>
       </c>
       <c r="C39">
@@ -911,6 +1061,11 @@
       </c>
     </row>
     <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Hidalgo</t>
+        </is>
+      </c>
       <c r="B40" t="inlineStr">
         <is>
           <t>Eloxochitlán</t>
@@ -924,6 +1079,11 @@
       </c>
     </row>
     <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Hidalgo</t>
+        </is>
+      </c>
       <c r="B41" t="inlineStr">
         <is>
           <t>Huichapan</t>
@@ -937,6 +1097,11 @@
       </c>
     </row>
     <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Hidalgo</t>
+        </is>
+      </c>
       <c r="B42" t="inlineStr">
         <is>
           <t>Pisaflores</t>
@@ -950,6 +1115,11 @@
       </c>
     </row>
     <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Hidalgo</t>
+        </is>
+      </c>
       <c r="B43" t="inlineStr">
         <is>
           <t>Tecozautla</t>
@@ -963,9 +1133,14 @@
       </c>
     </row>
     <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Hidalgo</t>
+        </is>
+      </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Tenango de Doria</t>
+          <t>Tenango De Doria</t>
         </is>
       </c>
       <c r="C44">
@@ -976,6 +1151,11 @@
       </c>
     </row>
     <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Hidalgo</t>
+        </is>
+      </c>
       <c r="B45" t="inlineStr">
         <is>
           <t>Total</t>
@@ -1007,6 +1187,11 @@
       </c>
     </row>
     <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B47" t="inlineStr">
         <is>
           <t>Jesús María</t>
@@ -1020,9 +1205,14 @@
       </c>
     </row>
     <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Ojuelos de Jalisco</t>
+          <t>Ojuelos De Jalisco</t>
         </is>
       </c>
       <c r="C48">
@@ -1033,6 +1223,11 @@
       </c>
     </row>
     <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B49" t="inlineStr">
         <is>
           <t>Teocaltiche</t>
@@ -1046,6 +1241,11 @@
       </c>
     </row>
     <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B50" t="inlineStr">
         <is>
           <t>Total</t>
@@ -1077,6 +1277,11 @@
       </c>
     </row>
     <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B52" t="inlineStr">
         <is>
           <t>Ocampo</t>
@@ -1090,6 +1295,11 @@
       </c>
     </row>
     <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B53" t="inlineStr">
         <is>
           <t>Paracho</t>
@@ -1103,6 +1313,11 @@
       </c>
     </row>
     <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B54" t="inlineStr">
         <is>
           <t>San Lucas</t>
@@ -1116,6 +1331,11 @@
       </c>
     </row>
     <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B55" t="inlineStr">
         <is>
           <t>Tzintzuntzan</t>
@@ -1129,6 +1349,11 @@
       </c>
     </row>
     <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B56" t="inlineStr">
         <is>
           <t>Zamora</t>
@@ -1142,6 +1367,11 @@
       </c>
     </row>
     <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B57" t="inlineStr">
         <is>
           <t>Total</t>
@@ -1173,6 +1403,11 @@
       </c>
     </row>
     <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Morelos</t>
+        </is>
+      </c>
       <c r="B59" t="inlineStr">
         <is>
           <t>Total</t>
@@ -1204,6 +1439,11 @@
       </c>
     </row>
     <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>Nayarit</t>
+        </is>
+      </c>
       <c r="B61" t="inlineStr">
         <is>
           <t>Total</t>
@@ -1224,7 +1464,7 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Acatlán de Pérez Figueroa</t>
+          <t>Acatlán De Pérez Figueroa</t>
         </is>
       </c>
       <c r="C62">
@@ -1235,6 +1475,11 @@
       </c>
     </row>
     <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B63" t="inlineStr">
         <is>
           <t>Matías Romero Avendaño</t>
@@ -1248,9 +1493,14 @@
       </c>
     </row>
     <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Nejapa de Madero</t>
+          <t>Nejapa De Madero</t>
         </is>
       </c>
       <c r="C64">
@@ -1261,9 +1511,14 @@
       </c>
     </row>
     <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Oaxaca de Juárez</t>
+          <t>Oaxaca De Juárez</t>
         </is>
       </c>
       <c r="C65">
@@ -1274,6 +1529,11 @@
       </c>
     </row>
     <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B66" t="inlineStr">
         <is>
           <t>San Agustín Loxicha</t>
@@ -1287,6 +1547,11 @@
       </c>
     </row>
     <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B67" t="inlineStr">
         <is>
           <t>San Juan Juquila Mixes</t>
@@ -1300,6 +1565,11 @@
       </c>
     </row>
     <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B68" t="inlineStr">
         <is>
           <t>San Juan Lalana</t>
@@ -1313,6 +1583,11 @@
       </c>
     </row>
     <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B69" t="inlineStr">
         <is>
           <t>San Lorenzo Texmelúcan</t>
@@ -1326,6 +1601,11 @@
       </c>
     </row>
     <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B70" t="inlineStr">
         <is>
           <t>San Miguel Quetzaltepec</t>
@@ -1339,6 +1619,11 @@
       </c>
     </row>
     <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B71" t="inlineStr">
         <is>
           <t>Santiago Amoltepec</t>
@@ -1352,6 +1637,11 @@
       </c>
     </row>
     <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B72" t="inlineStr">
         <is>
           <t>Santiago Camotlán</t>
@@ -1365,6 +1655,11 @@
       </c>
     </row>
     <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B73" t="inlineStr">
         <is>
           <t>Santiago Yosondúa</t>
@@ -1378,6 +1673,11 @@
       </c>
     </row>
     <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B74" t="inlineStr">
         <is>
           <t>Santo Domingo Ixcatlán</t>
@@ -1391,6 +1691,11 @@
       </c>
     </row>
     <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B75" t="inlineStr">
         <is>
           <t>Santos Reyes Nopala</t>
@@ -1404,6 +1709,11 @@
       </c>
     </row>
     <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B76" t="inlineStr">
         <is>
           <t>Silacayoápam</t>
@@ -1417,6 +1727,11 @@
       </c>
     </row>
     <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B77" t="inlineStr">
         <is>
           <t>Total</t>
@@ -1448,6 +1763,11 @@
       </c>
     </row>
     <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B79" t="inlineStr">
         <is>
           <t>Puebla</t>
@@ -1461,9 +1781,14 @@
       </c>
     </row>
     <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>San Salvador el Verde</t>
+          <t>San Salvador El Verde</t>
         </is>
       </c>
       <c r="C80">
@@ -1474,6 +1799,11 @@
       </c>
     </row>
     <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B81" t="inlineStr">
         <is>
           <t>Total</t>
@@ -1505,6 +1835,11 @@
       </c>
     </row>
     <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>Querétaro</t>
+        </is>
+      </c>
       <c r="B83" t="inlineStr">
         <is>
           <t>Total</t>
@@ -1536,6 +1871,11 @@
       </c>
     </row>
     <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>San Luis Potosí</t>
+        </is>
+      </c>
       <c r="B85" t="inlineStr">
         <is>
           <t>Matlapa</t>
@@ -1549,9 +1889,14 @@
       </c>
     </row>
     <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>San Luis Potosí</t>
+        </is>
+      </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>San Ciro de Acosta</t>
+          <t>San Ciro De Acosta</t>
         </is>
       </c>
       <c r="C86">
@@ -1562,6 +1907,11 @@
       </c>
     </row>
     <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>San Luis Potosí</t>
+        </is>
+      </c>
       <c r="B87" t="inlineStr">
         <is>
           <t>Total</t>
@@ -1593,6 +1943,11 @@
       </c>
     </row>
     <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>Tabasco</t>
+        </is>
+      </c>
       <c r="B89" t="inlineStr">
         <is>
           <t>Centro</t>
@@ -1606,6 +1961,11 @@
       </c>
     </row>
     <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>Tabasco</t>
+        </is>
+      </c>
       <c r="B90" t="inlineStr">
         <is>
           <t>Total</t>
@@ -1637,9 +1997,14 @@
       </c>
     </row>
     <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Hueyapan de Ocampo</t>
+          <t>Hueyapan De Ocampo</t>
         </is>
       </c>
       <c r="C92">
@@ -1650,6 +2015,11 @@
       </c>
     </row>
     <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B93" t="inlineStr">
         <is>
           <t>Misantla</t>
@@ -1663,6 +2033,11 @@
       </c>
     </row>
     <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B94" t="inlineStr">
         <is>
           <t>Papantla</t>
@@ -1676,6 +2051,11 @@
       </c>
     </row>
     <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B95" t="inlineStr">
         <is>
           <t>San Andrés Tuxtla</t>
@@ -1689,6 +2069,11 @@
       </c>
     </row>
     <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B96" t="inlineStr">
         <is>
           <t>Tamalín</t>
@@ -1702,6 +2087,11 @@
       </c>
     </row>
     <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B97" t="inlineStr">
         <is>
           <t>Álamo Temapache</t>
@@ -1715,6 +2105,11 @@
       </c>
     </row>
     <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B98" t="inlineStr">
         <is>
           <t>Zongolica</t>
@@ -1728,6 +2123,11 @@
       </c>
     </row>
     <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B99" t="inlineStr">
         <is>
           <t>Total</t>
@@ -1759,6 +2159,11 @@
       </c>
     </row>
     <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>Yucatán</t>
+        </is>
+      </c>
       <c r="B101" t="inlineStr">
         <is>
           <t>Total</t>
@@ -1782,41 +2187,6 @@
       </c>
       <c r="D102">
         <v>1</v>
-      </c>
-    </row>
-    <row r="104">
-      <c r="A104" t="inlineStr">
-        <is>
-          <t>Tamaño de la muestra: 566,547</t>
-        </is>
-      </c>
-    </row>
-    <row r="105">
-      <c r="A105" t="inlineStr">
-        <is>
-          <t>Fuente: Expedición de Matrículas Consulares de Alta Seguridad en los Consulados de México en E.E.U.U.</t>
-        </is>
-      </c>
-    </row>
-    <row r="106">
-      <c r="A106" t="inlineStr">
-        <is>
-          <t>Elaborado por: Análisis de Información, Instituto de los Mexicanos en el Exterior</t>
-        </is>
-      </c>
-    </row>
-    <row r="107">
-      <c r="A107" t="inlineStr">
-        <is>
-          <t>Secretaría de Relaciones Exteriores</t>
-        </is>
-      </c>
-    </row>
-    <row r="108">
-      <c r="A108" t="inlineStr">
-        <is>
-          <t>Mayo de 2023</t>
-        </is>
       </c>
     </row>
   </sheetData>
